--- a/Test_CheckList_Student_API.xlsx
+++ b/Test_CheckList_Student_API.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\Prj\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB508EB9-61DF-4BD3-8B93-1BFAC2CD1A27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{117F2AD0-BD7D-4BA1-8F6E-A90E719A2EA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tong quan" sheetId="1" r:id="rId1"/>
@@ -32,11 +32,6 @@
     <t>Student Club Management API - Test Checklist (Tiet 5: Test API tren Swagger/Postman)</t>
   </si>
   <si>
-    <t>Checklist kiem thu thu cong tren Swagger UI (/docs) hoac Postman, bao gom ca case dung (happy path) va case loi. Du an dung HTTPBearer (khong phai OAuth2PasswordBearer) nen KHONG co endpoint /auth/token: tren Swagger, bam nut Authorize va dan truc tiep access_token lay tu POST /auth/login vao o Value. Tren Postman: goi POST /auth/login (Form: email, password) de lay access_token, gan vao header Authorization: Bearer &lt;token&gt;.
-Quy uoc response: cac endpoint tao/sua (POST/PUT/PATCH) nhan du lieu dang Form (application/x-www-form-urlencoded), rieng upload file dung multipart/form-data (File). Moi response THANH CONG deu duoc boc envelope 6 truong {status_code, error, message, data, timestamp, path} - du lieu that nam trong data.
-Cac ket qua PASS/FAIL/PENDING duoi day da duoc XAC NHAN THUC TE bang cach dung server that (uvicorn + SQLite) va goi HTTP truc tiep toi tung endpoint (khong chi doc code suy doan), tuong duong voi viec chay bo test tu dong.</t>
-  </si>
-  <si>
     <t>Nhom</t>
   </si>
   <si>
@@ -239,9 +234,6 @@
   </si>
   <si>
     <t>Thieu header Authorization</t>
-  </si>
-  <si>
-    <t>Ghi chu chung:</t>
   </si>
   <si>
     <t>Du an nay dung HTTPBearer (khong phai OAuth2PasswordBearer) nen KHONG co endpoint /auth/token va nut Authorize tren Swagger se la 1 o nhap 'Bearer &lt;token&gt;' don gian (khong phai form username/password).
@@ -769,6 +761,14 @@
   </si>
   <si>
     <t>200, hoạt động của member đó hay assign_id vẫn còn tồn tại</t>
+  </si>
+  <si>
+    <t>Checklist kiểm thử thủ công trên Swagger UI (/docs) hoặc Postman, bao gồm cả case đúng (happy path) và case lỗi. Dự án dùng HTTPBearer (không phải OAuth2PasswordBearer) nên KHÔNG có endpoint /auth/token: trên Swagger, bấm nút Authorize và dán trực tiếp access_token lấy từ POST /auth/login vào ô Value. Trên Postman: gọi POST /auth/login (Form: email, password) để lấy access_token, gán vào header Authorization: Bearer &lt;token&gt;.
+Quy ước response: các endpoint tạo/sửa (POST/PUT/PATCH) nhận dữ liệu dạng Form (application/x-www-form-urlencoded), riêng upload file dùng multipart/form-data (File). Mọi response THÀNH CÔNG đều được bọc envelope 6 trường {status_code, error, message, data, timestamp, path} - dữ liệu thật nằm trong data.
+Các kết quả PASS/FAIL/PENDING dưới đây đã được XÁC NHẬN THỰC TẾ bằng cách dùng server thật (uvicorn + SQLite) và gọi HTTP trực tiếp tới từng endpoint (không chỉ đọc code suy đoán), tương đương với việc chạy bộ test tự động</t>
+  </si>
+  <si>
+    <t>Ghi chú chung</t>
   </si>
 </sst>
 </file>
@@ -942,6 +942,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -954,9 +957,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
@@ -1265,47 +1265,47 @@
     <col min="1" max="1" width="38" customWidth="1"/>
     <col min="2" max="3" width="10" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="5" max="5" width="54.796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
     </row>
     <row r="2" spans="1:5" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
+      <c r="A2" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
     </row>
     <row r="4" spans="1:5" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" s="2">
         <v>14</v>
@@ -1322,7 +1322,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" s="2">
         <v>5</v>
@@ -1339,7 +1339,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" s="2">
         <v>16</v>
@@ -1356,7 +1356,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" s="2">
         <v>10</v>
@@ -1373,7 +1373,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" s="2">
         <v>17</v>
@@ -1390,7 +1390,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" s="2">
         <v>9</v>
@@ -1407,7 +1407,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" s="2">
         <v>8</v>
@@ -1424,7 +1424,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B12" s="5">
         <v>79</v>
@@ -1440,67 +1440,67 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="14"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
+      <c r="A14" s="15"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="12"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
+      <c r="A15" s="13"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="12"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
+      <c r="A16" s="13"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="12"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
+      <c r="A17" s="13"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="12"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
+      <c r="A18" s="13"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
+      <c r="A19" s="13"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
+      <c r="A20" s="13"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
+      <c r="A21" s="13"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="12"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
+      <c r="A22" s="13"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1526,379 +1526,379 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="A1" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="3" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>20</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="C4" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="D4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>26</v>
-      </c>
       <c r="F4" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G4" s="7"/>
     </row>
     <row r="5" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>30</v>
-      </c>
       <c r="F5" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G5" s="7"/>
     </row>
     <row r="6" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="7" t="s">
-        <v>33</v>
-      </c>
       <c r="F6" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G6" s="7"/>
     </row>
     <row r="7" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>35</v>
-      </c>
       <c r="E7" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G7" s="7"/>
     </row>
     <row r="8" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="7" t="s">
+      <c r="E8" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="7" t="s">
-        <v>38</v>
-      </c>
       <c r="F8" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G8" s="7"/>
     </row>
     <row r="9" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="7" t="s">
+      <c r="E9" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="F9" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>41</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="7" t="s">
+      <c r="D10" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="E10" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="7" t="s">
-        <v>46</v>
-      </c>
       <c r="F10" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G10" s="7"/>
     </row>
     <row r="11" spans="1:7" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" s="7" t="s">
+      <c r="E11" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="F11" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>49</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" s="7" t="s">
+      <c r="E12" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E12" s="7" t="s">
-        <v>53</v>
-      </c>
       <c r="F12" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G12" s="7"/>
     </row>
     <row r="13" spans="1:7" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="7" t="s">
+      <c r="E13" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="7" t="s">
-        <v>56</v>
-      </c>
       <c r="F13" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G13" s="7"/>
     </row>
     <row r="14" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="7" t="s">
+      <c r="D14" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="E14" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>60</v>
-      </c>
       <c r="F14" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G14" s="7"/>
     </row>
     <row r="15" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" s="7" t="s">
+      <c r="E15" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E15" s="7" t="s">
-        <v>63</v>
-      </c>
       <c r="F15" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G15" s="7"/>
     </row>
     <row r="16" spans="1:7" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="C16" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="D16" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="D16" s="7" t="s">
-        <v>67</v>
-      </c>
       <c r="E16" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:7" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>69</v>
-      </c>
       <c r="E17" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G17" s="7"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>70</v>
+        <v>245</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
+      <c r="A20" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
+      <c r="A21" s="13"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="12"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
+      <c r="A22" s="13"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="12"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
+      <c r="A23" s="13"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1923,141 +1923,141 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="A1" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="3" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>20</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>75</v>
-      </c>
       <c r="F4" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G4" s="7"/>
     </row>
     <row r="5" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G5" s="7"/>
     </row>
     <row r="6" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>81</v>
-      </c>
       <c r="F6" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G6" s="7"/>
     </row>
     <row r="7" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>84</v>
-      </c>
       <c r="F7" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G7" s="7"/>
     </row>
     <row r="8" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" s="7" t="s">
+      <c r="E8" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>88</v>
-      </c>
       <c r="F8" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G8" s="7"/>
     </row>
@@ -2083,374 +2083,374 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="A1" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="3" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>20</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>92</v>
-      </c>
       <c r="F4" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G4" s="7"/>
     </row>
     <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G5" s="7"/>
     </row>
     <row r="6" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G6" s="7"/>
     </row>
     <row r="7" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>99</v>
-      </c>
       <c r="F7" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G7" s="7"/>
     </row>
     <row r="8" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" s="7" t="s">
+      <c r="E8" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>103</v>
-      </c>
       <c r="F8" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G8" s="7"/>
     </row>
     <row r="9" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>106</v>
-      </c>
       <c r="E9" s="7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G9" s="7"/>
     </row>
     <row r="10" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G10" s="7"/>
     </row>
     <row r="11" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>111</v>
-      </c>
       <c r="F11" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G11" s="7"/>
     </row>
     <row r="12" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>114</v>
-      </c>
       <c r="E12" s="7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G12" s="7"/>
     </row>
     <row r="13" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>117</v>
-      </c>
       <c r="E13" s="7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G13" s="7"/>
     </row>
     <row r="14" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>120</v>
-      </c>
       <c r="E14" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G14" s="7"/>
     </row>
     <row r="15" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>123</v>
-      </c>
       <c r="E15" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G15" s="7"/>
     </row>
     <row r="16" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:7" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="E17" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="D17" s="7" t="s">
+      <c r="F17" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="7" t="s">
         <v>126</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>131</v>
-      </c>
       <c r="F18" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G18" s="7"/>
     </row>
     <row r="19" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="D19" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C19" s="7" t="s">
+      <c r="E19" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="D19" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>135</v>
-      </c>
       <c r="F19" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G19" s="7"/>
     </row>
@@ -2476,246 +2476,246 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="A1" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="3" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>20</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>139</v>
-      </c>
       <c r="F4" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G4" s="7"/>
     </row>
     <row r="5" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G5" s="7"/>
     </row>
     <row r="6" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G6" s="7"/>
     </row>
     <row r="7" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G7" s="7"/>
     </row>
     <row r="8" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G8" s="7"/>
     </row>
     <row r="9" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G9" s="7"/>
     </row>
     <row r="10" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>152</v>
-      </c>
       <c r="E10" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G10" s="7"/>
     </row>
     <row r="11" spans="1:7" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G11" s="7"/>
     </row>
     <row r="12" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G12" s="7"/>
     </row>
     <row r="13" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>159</v>
-      </c>
       <c r="F13" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G13" s="7"/>
     </row>
@@ -2741,372 +2741,372 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="A1" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="3" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>20</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>163</v>
-      </c>
       <c r="F4" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G4" s="7"/>
     </row>
     <row r="5" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G5" s="7"/>
     </row>
     <row r="6" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G6" s="7"/>
     </row>
     <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>170</v>
-      </c>
       <c r="F7" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G7" s="7"/>
     </row>
     <row r="8" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G8" s="7"/>
     </row>
     <row r="9" spans="1:7" ht="43.2" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>175</v>
-      </c>
       <c r="F9" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G9" s="7"/>
     </row>
     <row r="10" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G10" s="7"/>
     </row>
     <row r="11" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G11" s="7"/>
     </row>
     <row r="12" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G12" s="7"/>
     </row>
     <row r="13" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G13" s="7"/>
     </row>
     <row r="14" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>186</v>
-      </c>
       <c r="E14" s="7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G14" s="7"/>
     </row>
     <row r="15" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G15" s="7"/>
     </row>
     <row r="16" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G17" s="7"/>
     </row>
     <row r="18" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G18" s="7"/>
     </row>
     <row r="19" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="E19" s="17">
+        <v>179</v>
+      </c>
+      <c r="E19" s="11">
         <v>404</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G19" s="7"/>
     </row>
@@ -3140,258 +3140,258 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="A1" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="3" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>20</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>198</v>
-      </c>
       <c r="E4" s="7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G4" s="7"/>
     </row>
     <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>201</v>
-      </c>
       <c r="F5" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G5" s="7"/>
     </row>
     <row r="6" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G6" s="7"/>
     </row>
     <row r="7" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G7" s="7"/>
     </row>
     <row r="8" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>208</v>
-      </c>
       <c r="E8" s="7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G8" s="7"/>
     </row>
     <row r="9" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G9" s="7"/>
     </row>
     <row r="10" spans="1:7" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="E10" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="D10" s="7" t="s">
+      <c r="F10" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="7" t="s">
         <v>212</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G11" s="7"/>
     </row>
     <row r="12" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="7"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="G12" s="7"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="15" t="s">
-        <v>219</v>
-      </c>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="12"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
+      <c r="A16" s="13"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="12"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
+      <c r="A17" s="13"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3416,188 +3416,188 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="A1" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="3" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>20</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>223</v>
-      </c>
       <c r="F4" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G4" s="7"/>
     </row>
     <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>227</v>
-      </c>
       <c r="F5" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G5" s="7"/>
     </row>
     <row r="6" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G6" s="7"/>
     </row>
     <row r="7" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G7" s="7"/>
     </row>
     <row r="8" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" s="7" t="s">
+      <c r="E8" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="7" t="s">
         <v>232</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" s="7" t="s">
+      <c r="E9" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>238</v>
-      </c>
       <c r="F9" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G9" s="7"/>
     </row>
     <row r="10" spans="1:7" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="E10" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="D10" s="7" t="s">
+      <c r="F10" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10" s="7" t="s">
         <v>241</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
